--- a/feature/enhance-sos/ig/ValueSet-sas-valueset-participant-status.xlsx
+++ b/feature/enhance-sos/ig/ValueSet-sas-valueset-participant-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T09:48:09+00:00</t>
+    <t>2026-07-15T12:35:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/enhance-sos/ig/ValueSet-sas-valueset-participant-status.xlsx
+++ b/feature/enhance-sos/ig/ValueSet-sas-valueset-participant-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T12:35:13+00:00</t>
+    <t>2026-07-15T17:12:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
